--- a/DesignTable/Data/Table/Tables/quest.xlsx
+++ b/DesignTable/Data/Table/Tables/quest.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Oh\Desktop\DesignGenerator\Data\Data_Export\Table\Tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{37027F7B-53E8-43E8-A58B-4583F5D38475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F6A54970-A2A7-45BE-87FC-F425B6101980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-240" yWindow="0" windowWidth="29040" windowHeight="15600" activeTab="1" xr2:uid="{6B0D3944-5E61-432C-B539-71B856D0F692}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{6B0D3944-5E61-432C-B539-71B856D0F692}"/>
   </bookViews>
   <sheets>
     <sheet name="record" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="28">
   <si>
     <t>ColumnName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -61,10 +61,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>TableID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>quest_Id</t>
   </si>
   <si>
@@ -122,6 +118,14 @@
   </si>
   <si>
     <t>reward_auto</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FieldNo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TableId</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -179,7 +183,11 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -194,7 +202,7 @@
 
 <file path=xl/xmlMaps.xml><?xml version="1.0" encoding="utf-8"?>
 <MapInfo xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" SelectionNamespaces="">
-  <Schema ID="Schema1">
+  <Schema ID="Schema2">
     <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="">
       <xsd:element nillable="true" name="quest">
         <xsd:complexType>
@@ -209,6 +217,7 @@
                 <xsd:attribute name="EnumID" form="unqualified" type="xsd:string"/>
                 <xsd:attribute name="IDRule" form="unqualified" type="xsd:string"/>
                 <xsd:attribute name="StringHashIds" form="unqualified" type="xsd:string"/>
+                <xsd:attribute name="FieldNo" form="unqualified" type="xsd:string"/>
                 <xsd:attribute name="TableId" form="unqualified" type="xsd:string"/>
               </xsd:complexType>
             </xsd:element>
@@ -229,7 +238,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="1" Name="quest_맵" RootElement="quest" SchemaID="Schema1" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="4" Name="quest_맵" RootElement="quest" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -238,22 +247,22 @@
   <autoFilter ref="A1:F2" xr:uid="{38A53545-E920-404C-82D5-0E71EFC6A6B4}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{784865AD-E21D-469F-9782-8264DFDF4DE5}" uniqueName="quest_Id" name="quest_Id">
-      <xmlColumnPr mapId="1" xpath="/quest/record/quest_Id" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/quest/record/quest_Id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{303EAC3C-1EF2-40FB-A174-E10921B97AE9}" uniqueName="quest_type" name="quest_type">
-      <xmlColumnPr mapId="1" xpath="/quest/record/quest_type" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/quest/record/quest_type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{8CAA14AE-C939-49B8-B8B2-CC458E17EEE2}" uniqueName="reward" name="reward">
-      <xmlColumnPr mapId="1" xpath="/quest/record/reward" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/quest/record/reward" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{8FCC1EF5-5EE4-4435-833C-0224359EF690}" uniqueName="quest_target" name="quest_target">
-      <xmlColumnPr mapId="1" xpath="/quest/record/quest_target" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/quest/record/quest_target" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{FCDF0E66-E70F-42D3-B995-C7C000857EA2}" uniqueName="quest_description" name="quest_description">
-      <xmlColumnPr mapId="1" xpath="/quest/record/quest_description" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/quest/record/quest_description" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{3AAFC501-DBD1-496A-A00B-B2BEAB3CF96F}" uniqueName="reward_auto" name="reward_auto">
-      <xmlColumnPr mapId="1" xpath="/quest/record/reward_auto" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/quest/record/reward_auto" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -261,35 +270,38 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69842AAB-D29A-4FF2-A42E-05B17AF27C97}" name="표1" displayName="표1" ref="A1:I7" tableType="xml" totalsRowShown="0">
-  <autoFilter ref="A1:I7" xr:uid="{69842AAB-D29A-4FF2-A42E-05B17AF27C97}"/>
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69842AAB-D29A-4FF2-A42E-05B17AF27C97}" name="표1" displayName="표1" ref="A1:J7" tableType="xml" totalsRowShown="0">
+  <autoFilter ref="A1:J7" xr:uid="{69842AAB-D29A-4FF2-A42E-05B17AF27C97}"/>
+  <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{5A7AEF9A-7AC9-4220-BFFA-87B0B4A046B2}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="1" xpath="/quest/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/quest/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{9C876816-3252-448A-89CF-7C3E287E932B}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="1" xpath="/quest/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/quest/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{73A1B43A-2479-4F98-AB58-F21B64E23297}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="1" xpath="/quest/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/quest/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{8351D407-539F-4883-9368-428C3EE561FA}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="1" xpath="/quest/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/quest/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{0D80BB31-0853-42E2-91B5-4D12F1542503}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="1" xpath="/quest/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/quest/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{A25957F7-46FE-42BC-BFC6-406D71060749}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="1" xpath="/quest/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/quest/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{B141F435-29ED-448E-AD85-B53DD686DD7B}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="1" xpath="/quest/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/quest/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{CFE5E2F0-41A1-4F07-92D8-44FC9BFA538B}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="1" xpath="/quest/verify/@StringHashIds" xmlDataType="string"/>
-    </tableColumn>
-    <tableColumn id="9" xr3:uid="{6EDD528A-EC1C-4535-85D6-B86E885932DA}" uniqueName="TableId" name="TableID">
-      <xmlColumnPr mapId="1" xpath="/quest/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/quest/verify/@StringHashIds" xmlDataType="string"/>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{6EDD528A-EC1C-4535-85D6-B86E885932DA}" uniqueName="FieldNo" name="FieldNo">
+      <xmlColumnPr mapId="4" xpath="/quest/verify/@FieldNo" xmlDataType="string"/>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{D4F06751-C70A-4C28-B6F9-D88832B50590}" uniqueName="TableId" name="TableId" dataDxfId="0">
+      <xmlColumnPr mapId="4" xpath="/quest/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -598,22 +610,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -635,10 +647,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{424D4E64-2AF7-4D09-B118-D007ED1290F1}">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -664,180 +676,201 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="1">
+        <v>1020</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="1">
+      <c r="C3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="1">
         <v>1020</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" s="1">
+      <c r="F4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="1">
         <v>1020</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" s="1">
+      <c r="C5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5" s="1">
         <v>1020</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="1">
+      <c r="B6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J6" s="1">
         <v>1020</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1020</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="C7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I7" s="1">
+        <v>11</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J7" s="1">
         <v>1020</v>
       </c>
     </row>

--- a/DesignTable/Data/Table/Tables/quest.xlsx
+++ b/DesignTable/Data/Table/Tables/quest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F6A54970-A2A7-45BE-87FC-F425B6101980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{67EF9DEA-BC51-4F6E-9F0E-31B1DF43143A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{6B0D3944-5E61-432C-B539-71B856D0F692}"/>
   </bookViews>
@@ -238,7 +238,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="4" Name="quest_맵" RootElement="quest" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="6" Name="quest_맵" RootElement="quest" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -247,22 +247,22 @@
   <autoFilter ref="A1:F2" xr:uid="{38A53545-E920-404C-82D5-0E71EFC6A6B4}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{784865AD-E21D-469F-9782-8264DFDF4DE5}" uniqueName="quest_Id" name="quest_Id">
-      <xmlColumnPr mapId="4" xpath="/quest/record/quest_Id" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/quest/record/quest_Id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{303EAC3C-1EF2-40FB-A174-E10921B97AE9}" uniqueName="quest_type" name="quest_type">
-      <xmlColumnPr mapId="4" xpath="/quest/record/quest_type" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/quest/record/quest_type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{8CAA14AE-C939-49B8-B8B2-CC458E17EEE2}" uniqueName="reward" name="reward">
-      <xmlColumnPr mapId="4" xpath="/quest/record/reward" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/quest/record/reward" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{8FCC1EF5-5EE4-4435-833C-0224359EF690}" uniqueName="quest_target" name="quest_target">
-      <xmlColumnPr mapId="4" xpath="/quest/record/quest_target" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/quest/record/quest_target" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{FCDF0E66-E70F-42D3-B995-C7C000857EA2}" uniqueName="quest_description" name="quest_description">
-      <xmlColumnPr mapId="4" xpath="/quest/record/quest_description" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/quest/record/quest_description" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{3AAFC501-DBD1-496A-A00B-B2BEAB3CF96F}" uniqueName="reward_auto" name="reward_auto">
-      <xmlColumnPr mapId="4" xpath="/quest/record/reward_auto" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/quest/record/reward_auto" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -274,34 +274,34 @@
   <autoFilter ref="A1:J7" xr:uid="{69842AAB-D29A-4FF2-A42E-05B17AF27C97}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{5A7AEF9A-7AC9-4220-BFFA-87B0B4A046B2}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="4" xpath="/quest/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/quest/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{9C876816-3252-448A-89CF-7C3E287E932B}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="4" xpath="/quest/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/quest/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{73A1B43A-2479-4F98-AB58-F21B64E23297}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="4" xpath="/quest/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/quest/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{8351D407-539F-4883-9368-428C3EE561FA}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="4" xpath="/quest/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/quest/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{0D80BB31-0853-42E2-91B5-4D12F1542503}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="4" xpath="/quest/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/quest/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{A25957F7-46FE-42BC-BFC6-406D71060749}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="4" xpath="/quest/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/quest/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{B141F435-29ED-448E-AD85-B53DD686DD7B}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="4" xpath="/quest/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/quest/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{CFE5E2F0-41A1-4F07-92D8-44FC9BFA538B}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="4" xpath="/quest/verify/@StringHashIds" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/quest/verify/@StringHashIds" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{6EDD528A-EC1C-4535-85D6-B86E885932DA}" uniqueName="FieldNo" name="FieldNo">
-      <xmlColumnPr mapId="4" xpath="/quest/verify/@FieldNo" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/quest/verify/@FieldNo" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{D4F06751-C70A-4C28-B6F9-D88832B50590}" uniqueName="TableId" name="TableId" dataDxfId="0">
-      <xmlColumnPr mapId="4" xpath="/quest/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/quest/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>

--- a/DesignTable/Data/Table/Tables/quest.xlsx
+++ b/DesignTable/Data/Table/Tables/quest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{67EF9DEA-BC51-4F6E-9F0E-31B1DF43143A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A30F7C4E-3596-47A9-98E1-AA6DA0057B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{6B0D3944-5E61-432C-B539-71B856D0F692}"/>
   </bookViews>
@@ -238,7 +238,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="6" Name="quest_맵" RootElement="quest" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="8" Name="quest_맵" RootElement="quest" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -247,22 +247,22 @@
   <autoFilter ref="A1:F2" xr:uid="{38A53545-E920-404C-82D5-0E71EFC6A6B4}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{784865AD-E21D-469F-9782-8264DFDF4DE5}" uniqueName="quest_Id" name="quest_Id">
-      <xmlColumnPr mapId="6" xpath="/quest/record/quest_Id" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/quest/record/quest_Id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{303EAC3C-1EF2-40FB-A174-E10921B97AE9}" uniqueName="quest_type" name="quest_type">
-      <xmlColumnPr mapId="6" xpath="/quest/record/quest_type" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/quest/record/quest_type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{8CAA14AE-C939-49B8-B8B2-CC458E17EEE2}" uniqueName="reward" name="reward">
-      <xmlColumnPr mapId="6" xpath="/quest/record/reward" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/quest/record/reward" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{8FCC1EF5-5EE4-4435-833C-0224359EF690}" uniqueName="quest_target" name="quest_target">
-      <xmlColumnPr mapId="6" xpath="/quest/record/quest_target" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/quest/record/quest_target" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{FCDF0E66-E70F-42D3-B995-C7C000857EA2}" uniqueName="quest_description" name="quest_description">
-      <xmlColumnPr mapId="6" xpath="/quest/record/quest_description" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/quest/record/quest_description" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{3AAFC501-DBD1-496A-A00B-B2BEAB3CF96F}" uniqueName="reward_auto" name="reward_auto">
-      <xmlColumnPr mapId="6" xpath="/quest/record/reward_auto" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/quest/record/reward_auto" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -274,34 +274,34 @@
   <autoFilter ref="A1:J7" xr:uid="{69842AAB-D29A-4FF2-A42E-05B17AF27C97}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{5A7AEF9A-7AC9-4220-BFFA-87B0B4A046B2}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="6" xpath="/quest/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/quest/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{9C876816-3252-448A-89CF-7C3E287E932B}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="6" xpath="/quest/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/quest/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{73A1B43A-2479-4F98-AB58-F21B64E23297}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="6" xpath="/quest/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/quest/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{8351D407-539F-4883-9368-428C3EE561FA}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="6" xpath="/quest/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/quest/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{0D80BB31-0853-42E2-91B5-4D12F1542503}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="6" xpath="/quest/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/quest/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{A25957F7-46FE-42BC-BFC6-406D71060749}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="6" xpath="/quest/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/quest/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{B141F435-29ED-448E-AD85-B53DD686DD7B}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="6" xpath="/quest/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/quest/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{CFE5E2F0-41A1-4F07-92D8-44FC9BFA538B}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="6" xpath="/quest/verify/@StringHashIds" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/quest/verify/@StringHashIds" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{6EDD528A-EC1C-4535-85D6-B86E885932DA}" uniqueName="FieldNo" name="FieldNo">
-      <xmlColumnPr mapId="6" xpath="/quest/verify/@FieldNo" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/quest/verify/@FieldNo" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{D4F06751-C70A-4C28-B6F9-D88832B50590}" uniqueName="TableId" name="TableId" dataDxfId="0">
-      <xmlColumnPr mapId="6" xpath="/quest/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/quest/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>

--- a/DesignTable/Data/Table/Tables/quest.xlsx
+++ b/DesignTable/Data/Table/Tables/quest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A30F7C4E-3596-47A9-98E1-AA6DA0057B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F529151-736C-44C7-86E3-F54257DBA459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{6B0D3944-5E61-432C-B539-71B856D0F692}"/>
   </bookViews>
@@ -238,7 +238,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="8" Name="quest_맵" RootElement="quest" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="9" Name="quest_맵" RootElement="quest" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -247,22 +247,22 @@
   <autoFilter ref="A1:F2" xr:uid="{38A53545-E920-404C-82D5-0E71EFC6A6B4}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{784865AD-E21D-469F-9782-8264DFDF4DE5}" uniqueName="quest_Id" name="quest_Id">
-      <xmlColumnPr mapId="8" xpath="/quest/record/quest_Id" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/quest/record/quest_Id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{303EAC3C-1EF2-40FB-A174-E10921B97AE9}" uniqueName="quest_type" name="quest_type">
-      <xmlColumnPr mapId="8" xpath="/quest/record/quest_type" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/quest/record/quest_type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{8CAA14AE-C939-49B8-B8B2-CC458E17EEE2}" uniqueName="reward" name="reward">
-      <xmlColumnPr mapId="8" xpath="/quest/record/reward" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/quest/record/reward" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{8FCC1EF5-5EE4-4435-833C-0224359EF690}" uniqueName="quest_target" name="quest_target">
-      <xmlColumnPr mapId="8" xpath="/quest/record/quest_target" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/quest/record/quest_target" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{FCDF0E66-E70F-42D3-B995-C7C000857EA2}" uniqueName="quest_description" name="quest_description">
-      <xmlColumnPr mapId="8" xpath="/quest/record/quest_description" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/quest/record/quest_description" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{3AAFC501-DBD1-496A-A00B-B2BEAB3CF96F}" uniqueName="reward_auto" name="reward_auto">
-      <xmlColumnPr mapId="8" xpath="/quest/record/reward_auto" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/quest/record/reward_auto" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -274,34 +274,34 @@
   <autoFilter ref="A1:J7" xr:uid="{69842AAB-D29A-4FF2-A42E-05B17AF27C97}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{5A7AEF9A-7AC9-4220-BFFA-87B0B4A046B2}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="8" xpath="/quest/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/quest/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{9C876816-3252-448A-89CF-7C3E287E932B}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="8" xpath="/quest/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/quest/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{73A1B43A-2479-4F98-AB58-F21B64E23297}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="8" xpath="/quest/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/quest/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{8351D407-539F-4883-9368-428C3EE561FA}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="8" xpath="/quest/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/quest/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{0D80BB31-0853-42E2-91B5-4D12F1542503}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="8" xpath="/quest/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/quest/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{A25957F7-46FE-42BC-BFC6-406D71060749}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="8" xpath="/quest/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/quest/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{B141F435-29ED-448E-AD85-B53DD686DD7B}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="8" xpath="/quest/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/quest/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{CFE5E2F0-41A1-4F07-92D8-44FC9BFA538B}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="8" xpath="/quest/verify/@StringHashIds" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/quest/verify/@StringHashIds" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{6EDD528A-EC1C-4535-85D6-B86E885932DA}" uniqueName="FieldNo" name="FieldNo">
-      <xmlColumnPr mapId="8" xpath="/quest/verify/@FieldNo" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/quest/verify/@FieldNo" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{D4F06751-C70A-4C28-B6F9-D88832B50590}" uniqueName="TableId" name="TableId" dataDxfId="0">
-      <xmlColumnPr mapId="8" xpath="/quest/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/quest/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
